--- a/untranslated/downloads/data-excel/4.b.1.1.xlsx
+++ b/untranslated/downloads/data-excel/4.b.1.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F05A01C-7EBD-41B4-A72B-0E321C7AA970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -109,13 +110,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -182,39 +191,50 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{99F0C6A2-4562-452D-BF60-54A469BFFE6F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -230,9 +250,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -270,9 +290,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -307,7 +327,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -342,7 +362,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -515,15 +535,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="40.85546875" customWidth="1"/>
     <col min="4" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,7 +560,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -557,7 +577,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -571,8 +591,9 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N3" s="12"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -612,8 +633,11 @@
       <c r="M4" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="11">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -653,8 +677,11 @@
       <c r="M5" s="2">
         <v>700</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="10">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -694,8 +721,11 @@
       <c r="M6" s="7">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -735,8 +765,11 @@
       <c r="M7" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -776,8 +809,11 @@
       <c r="M8" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -817,8 +853,11 @@
       <c r="M9" s="2">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N9" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
@@ -858,8 +897,11 @@
       <c r="M10" s="4">
         <v>143</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="12">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
